--- a/artfynd/A 17333-2021 artfynd.xlsx
+++ b/artfynd/A 17333-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17333-2021 artfynd.xlsx
+++ b/artfynd/A 17333-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>64916318</v>
       </c>
       <c r="B2" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594514.2561160453</v>
+        <v>594514</v>
       </c>
       <c r="R2" t="n">
-        <v>6950746.297087863</v>
+        <v>6950746</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -759,19 +754,9 @@
           <t>2017-04-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 17333-2021 artfynd.xlsx
+++ b/artfynd/A 17333-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64916318</v>
       </c>
       <c r="B2" t="n">
-        <v>57674</v>
+        <v>57676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17333-2021 artfynd.xlsx
+++ b/artfynd/A 17333-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64916318</v>
       </c>
       <c r="B2" t="n">
-        <v>57676</v>
+        <v>57679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17333-2021 artfynd.xlsx
+++ b/artfynd/A 17333-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64916318</v>
       </c>
       <c r="B2" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17333-2021 artfynd.xlsx
+++ b/artfynd/A 17333-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64916318</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17333-2021 artfynd.xlsx
+++ b/artfynd/A 17333-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64916318</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
